--- a/export_templates/dp_solid_checksheet.xlsx
+++ b/export_templates/dp_solid_checksheet.xlsx
@@ -32121,9 +32121,7 @@
         <v>All teammates stated that, at least, safety manager and site leadership representative (e.g. plant manager, department manager, line manager) was involved in the root cause analysis process when a serious incident(lost-time-injury, etc.) occurred.
 (Leadership: Operator: No.5)</v>
       </c>
-      <c r="J4" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J4" s="24"/>
       <c r="K4" s="140"/>
       <c r="L4" s="140"/>
       <c r="M4" s="140"/>
@@ -32147,9 +32145,7 @@
         <v>All teammates can state that they are informed of recent safety incidents (injury, near-miss, etc.) in their areas and actions have been taken to address these.
 (Teammate Engagement: Operator: No.7)</v>
       </c>
-      <c r="J5" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J5" s="24"/>
       <c r="K5" s="140"/>
       <c r="L5" s="140"/>
       <c r="M5" s="140"/>
@@ -32177,9 +32173,7 @@
 (System: Operator: No.64)
  *information: injury, near-miss etc.</v>
       </c>
-      <c r="J6" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J6" s="24"/>
       <c r="K6" s="140"/>
       <c r="L6" s="140"/>
       <c r="M6" s="140"/>
@@ -32203,9 +32197,7 @@
         <v>Teammates can provide examples of accidents which occurred on other facilities and how that information was obtained. 
 (System: Operator: No.110)</v>
       </c>
-      <c r="J7" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J7" s="24"/>
       <c r="K7" s="140"/>
       <c r="L7" s="140"/>
       <c r="M7" s="140"/>
@@ -32229,9 +32221,7 @@
         <v>H&amp;S risks/measures of other departments have been shared at the safety meeting in your department.
 (Teammate Engagement: Operator: No.17)</v>
       </c>
-      <c r="J8" s="24" t="s">
-        <v>654</v>
-      </c>
+      <c r="J8" s="24"/>
       <c r="K8" s="140"/>
       <c r="L8" s="140"/>
       <c r="M8" s="140"/>
@@ -32257,9 +32247,7 @@
         <v>A sample of 3 teammates, at least 1 (more than 33%) said they take part in the actions required to prevent safety accidents and provide feedback if these actions are not appropriate or useful. 
 (Teammate Engagement: Operator: No.6)</v>
       </c>
-      <c r="J9" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J9" s="59"/>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
       <c r="M9" s="30"/>
@@ -32286,9 +32274,7 @@
         <v>All teammates stated that management had taken specific actions to address hazards they reported, and these actions have been communicated to them. (safety point of view)
 (Organization: Operator: No.16)</v>
       </c>
-      <c r="J10" s="59" t="s">
-        <v>654</v>
-      </c>
+      <c r="J10" s="59"/>
       <c r="K10" s="30"/>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
@@ -32322,9 +32308,7 @@
         <v>The respondent is able to provide at least one recent example of bottom-up communication on hazards and risks.
 (System: Safety Manager: No.95)</v>
       </c>
-      <c r="J11" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J11" s="59"/>
       <c r="K11" s="30"/>
       <c r="L11" s="30"/>
       <c r="M11" s="30"/>
@@ -32353,9 +32337,7 @@
 And, operator take one's own key and locks to GENBA if it is necessary.
 (operator)</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J12" s="12"/>
       <c r="K12" s="141"/>
       <c r="L12" s="141"/>
       <c r="M12" s="141"/>
@@ -32383,9 +32365,7 @@
  *ECP should be prepared for all LOTO devise
 (Operator)</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J13" s="12"/>
       <c r="K13" s="141"/>
       <c r="L13" s="141"/>
       <c r="M13" s="141"/>
@@ -32412,9 +32392,7 @@
 If the operator do not handle LOTO, he/she can explain basic LOTO rule.
 (Operator)</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J14" s="12"/>
       <c r="K14" s="141"/>
       <c r="L14" s="141"/>
       <c r="M14" s="141"/>
@@ -32445,9 +32423,7 @@
         <v>All teammates are taking BSFA training more than annually.
 (Operator)</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J15" s="12"/>
       <c r="K15" s="141"/>
       <c r="L15" s="141"/>
       <c r="M15" s="141"/>
@@ -32476,9 +32452,7 @@
 And, self-check has been implemented.
 (System: Operator: No.19)</v>
       </c>
-      <c r="J16" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J16" s="24"/>
       <c r="K16" s="140"/>
       <c r="L16" s="140"/>
       <c r="M16" s="140"/>
@@ -32502,9 +32476,7 @@
   *work area: production area and office
 (System: Operator: No.75)</v>
       </c>
-      <c r="J17" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J17" s="24"/>
       <c r="K17" s="140"/>
       <c r="L17" s="140"/>
       <c r="M17" s="140"/>
@@ -32527,9 +32499,7 @@
         <v>3S activity for the improvement of 3S level has been  proceeded. (or Improvement of 3S level can be confirmed, or 3s level is over 4.)
 (System: Operator: No.105)</v>
       </c>
-      <c r="J18" s="24" t="s">
-        <v>654</v>
-      </c>
+      <c r="J18" s="24"/>
       <c r="K18" s="140"/>
       <c r="L18" s="140"/>
       <c r="M18" s="140"/>
@@ -32672,9 +32642,7 @@
         <v>All teammates recognize the H&amp;S risks applicable in their areas and confirmed these were addressed in trainings. 
 (Teammate Engagement: Operator: No.1)</v>
       </c>
-      <c r="J23" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J23" s="24"/>
       <c r="K23" s="140"/>
       <c r="L23" s="140"/>
       <c r="M23" s="140"/>
@@ -32700,9 +32668,7 @@
         <v>A sample of 3 teammates could all state that they took the traning on residual risks based on the work standard.
 (Teammate Engagement: Operator: No.11)</v>
       </c>
-      <c r="J24" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J24" s="24"/>
       <c r="K24" s="140"/>
       <c r="L24" s="140"/>
       <c r="M24" s="140"/>
@@ -32728,9 +32694,7 @@
         <v>A sample of 3 teammates could all describe and explain the greatest potential H&amp;S risks in their work, and what controls they use or are in place to mitigate these risks.
 (Teammate Engagement: Operator: No.13)</v>
       </c>
-      <c r="J25" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J25" s="24"/>
       <c r="K25" s="140"/>
       <c r="L25" s="140"/>
       <c r="M25" s="140"/>
@@ -32756,9 +32720,7 @@
         <v>In a sample of 3 teammates, at least one have participated RA process, and he/she could explain a full and accurate Risk Assessment.
 (Teammate Engagement: Operator: No.14)</v>
       </c>
-      <c r="J26" s="24" t="s">
-        <v>654</v>
-      </c>
+      <c r="J26" s="24"/>
       <c r="K26" s="140"/>
       <c r="L26" s="140"/>
       <c r="M26" s="140"/>
@@ -32784,9 +32746,7 @@
         <v>H&amp;S risks/measures of other departments have been shared at the safety meeting in your department.
 (Teammate Engagement: Operator: No.17)</v>
       </c>
-      <c r="J27" s="24" t="s">
-        <v>654</v>
-      </c>
+      <c r="J27" s="24"/>
       <c r="K27" s="140"/>
       <c r="L27" s="140"/>
       <c r="M27" s="140"/>
@@ -32814,9 +32774,7 @@
         <v>All operators shows understanding of the applicable All Bridgestone Safety Rules in their areas.
 (System: Operator: No.13)</v>
       </c>
-      <c r="J28" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J28" s="24"/>
       <c r="K28" s="140"/>
       <c r="L28" s="140"/>
       <c r="M28" s="140"/>
@@ -32842,9 +32800,7 @@
         <v>All teammates can demonstrate knowledge of the Safety Rules and explain key points on safety in the work standard.
 (System: Operator: No.70)</v>
       </c>
-      <c r="J29" s="24" t="s">
-        <v>654</v>
-      </c>
+      <c r="J29" s="24"/>
       <c r="K29" s="140"/>
       <c r="L29" s="140"/>
       <c r="M29" s="140"/>
@@ -32871,9 +32827,7 @@
 （Examples of FB: Responsed to proposed safety rules. Teammates can work based on the safety rules, or require changes due to dificulties to work based on the rules, etc.)
 (System: Operator: No.128)</v>
       </c>
-      <c r="J30" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J30" s="24"/>
       <c r="K30" s="140"/>
       <c r="L30" s="140"/>
       <c r="M30" s="140"/>
@@ -57580,9 +57534,7 @@
         <v>Issuing injury report with SBU's support.
 (Safety Manager)</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:11" ht="74.5" customHeight="1">
       <c r="C8" s="548"/>
@@ -57601,9 +57553,7 @@
         <v>Injury report is issued by plant, but there was a delay in the due date in the guideline.
 (Safety Manager)</v>
       </c>
-      <c r="J8" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J8" s="12"/>
     </row>
     <row r="9" spans="2:11" ht="74.5" customHeight="1">
       <c r="C9" s="548"/>
@@ -57623,9 +57573,7 @@
 And root cause analysis and its countermeasure has been completed and these report is issued within the due date as the guideline.
 (Safety Manager)</v>
       </c>
-      <c r="J9" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J9" s="12"/>
     </row>
     <row r="10" spans="2:11" ht="74.5" customHeight="1">
       <c r="C10" s="548"/>
@@ -57646,9 +57594,7 @@
 Also, the countermeasure has been spreaded to similar machines/tasks. After the countermeasure is compleated, the report to SBU has been issued. 
 (Safety Manager)</v>
       </c>
-      <c r="J10" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J10" s="12"/>
     </row>
     <row r="11" spans="2:11" ht="74.5" customHeight="1">
       <c r="C11" s="548"/>
@@ -57692,9 +57638,7 @@
  *"Countermeasure" in this part means that is issued from BSJ7310
 (Safety Manager)</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:11" ht="49.5">
       <c r="C13" s="548"/>
@@ -57714,9 +57658,7 @@
  *No corrective plan for delay.
 (Safety Manager)</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:11" ht="49.5">
       <c r="C14" s="548"/>
@@ -57736,9 +57678,7 @@
 Or, there is a delay but corrective plan has been made for it, and it is on-going.
 (Safety Manager)</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:11" ht="33">
       <c r="C15" s="548"/>
@@ -57757,9 +57697,7 @@
         <v>There is a plan for contermeasure, and progressing ahead of the plan, but not yet completed.
 (Safety Manager)</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:11" ht="33">
       <c r="C16" s="556"/>
@@ -57778,9 +57716,7 @@
         <v>All contermeasures have been completed.
 (Safety Manager)</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" spans="3:11" ht="33">
       <c r="C17" s="550" t="s">
@@ -57807,9 +57743,7 @@
         <v>Safety policy/target has not been issued.
 (Safety Manager)</v>
       </c>
-      <c r="J17" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" spans="3:11" ht="33">
       <c r="C18" s="550"/>
@@ -57828,9 +57762,7 @@
         <v>There is evidence of OH&amp;S benchmarking with other sites.
 (System: Safety Manager: No.123)</v>
       </c>
-      <c r="J18" s="29" t="s">
-        <v>654</v>
-      </c>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="3:11" ht="49.5">
       <c r="C19" s="550"/>
@@ -57851,9 +57783,7 @@
         <v>There is no implementation plan for safety.
 (Safety Manager)</v>
       </c>
-      <c r="J19" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="3:11" ht="33">
       <c r="C20" s="550"/>
@@ -57874,9 +57804,7 @@
         <v>Internal/external audit has not been conducted.
 (Safety Manager)</v>
       </c>
-      <c r="J20" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J20" s="59"/>
     </row>
     <row r="21" spans="3:11" ht="49.5">
       <c r="C21" s="550"/>
@@ -57895,9 +57823,7 @@
         <v>Internal audit has been conducted, and its report could be found. But, it is not enough to follow up the findings.
 (System: Safety Manager: No.47)</v>
       </c>
-      <c r="J21" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J21" s="59"/>
     </row>
     <row r="22" spans="3:11" ht="33">
       <c r="C22" s="550"/>
@@ -57916,9 +57842,7 @@
         <v>Items/Non-Conformities pointed out at the internal audits were improved or planed to improve them.
 (System: Safety Manager: No.77)</v>
       </c>
-      <c r="J22" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J22" s="59"/>
     </row>
     <row r="23" spans="3:11" ht="33">
       <c r="C23" s="550"/>
@@ -57937,9 +57861,7 @@
         <v>OFIs found at last internal audit have been improved or have been planed to improve.
 (System: Safety Manager: No.106)</v>
       </c>
-      <c r="J23" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J23" s="59"/>
     </row>
     <row r="24" spans="3:11" ht="49.5">
       <c r="C24" s="550"/>
@@ -57958,9 +57880,7 @@
         <v>Regarding the safety management system in the plant, the H&amp;S manager can explain evaluation results by third party, feedback, and the actions.
 (Organization: Safety Manager: No.20)</v>
       </c>
-      <c r="J24" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J24" s="59"/>
     </row>
     <row r="25" spans="3:11" ht="33">
       <c r="C25" s="550" t="s">
@@ -57987,9 +57907,7 @@
         <v>All teammates are taking BSFA training more than annually, but the material is not the latest version.
 (Safety Manager)</v>
       </c>
-      <c r="J25" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" spans="3:11" ht="82.5">
       <c r="C26" s="550"/>
@@ -58010,9 +57928,7 @@
  *In case that the material is not updated, if the site have a plan for the training, this item could be judged "Yes".
 (Safety Manager)</v>
       </c>
-      <c r="J26" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" spans="3:11" ht="49.5">
       <c r="C27" s="550"/>
@@ -58031,9 +57947,7 @@
         <v>After the BSFA training, all teammates' understandings are validated in GENBA situation by manager or supervisor.
 (Safety Manager)</v>
       </c>
-      <c r="J27" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" spans="3:11" ht="49.5">
       <c r="C28" s="550"/>
@@ -58052,9 +57966,7 @@
         <v>After the BSFA training, all teammates' understandings are validated in GENBA situation by manager or supervisor, and all teammates could answer correctly. 
 (Safety Manager)</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" spans="3:11" ht="49.5">
       <c r="C29" s="550"/>
@@ -58075,9 +57987,7 @@
         <v>The best practices on 3S have been gathered from other plants/industry, and it has been incorporated into the site procedure. or There is a evidence of the comparison with other plants.
 (System: Safety Manager: No.133)</v>
       </c>
-      <c r="J29" s="24" t="s">
-        <v>654</v>
-      </c>
+      <c r="J29" s="24"/>
       <c r="K29" t="s">
         <v>657</v>
       </c>
@@ -58101,9 +58011,7 @@
         <v>4M change process is standardized/documented at the site.
 (Safety Manager)</v>
       </c>
-      <c r="J30" s="62" t="s">
-        <v>651</v>
-      </c>
+      <c r="J30" s="62"/>
     </row>
     <row r="31" spans="3:11" ht="49.5">
       <c r="C31" s="550"/>
@@ -58122,9 +58030,7 @@
         <v>4M change process is standardized/documented at the site, and EHS manager confirm/approve it as a system.
 (Safety Manager)</v>
       </c>
-      <c r="J31" s="62" t="s">
-        <v>651</v>
-      </c>
+      <c r="J31" s="62"/>
     </row>
     <row r="32" spans="3:11" ht="66">
       <c r="C32" s="550"/>
@@ -58144,9 +58050,7 @@
  *at leastt one example should be validated
 (Safety Manager)</v>
       </c>
-      <c r="J32" s="62" t="s">
-        <v>651</v>
-      </c>
+      <c r="J32" s="62"/>
     </row>
     <row r="33" spans="3:10" ht="49.5">
       <c r="C33" s="550"/>
@@ -58165,9 +58069,7 @@
         <v>The changing point is valiadted not only by documents documents or pictures, but by GENBA validation.
 (Safety Manager)</v>
       </c>
-      <c r="J33" s="62" t="s">
-        <v>651</v>
-      </c>
+      <c r="J33" s="62"/>
     </row>
     <row r="34" spans="3:10" ht="33">
       <c r="C34" s="550"/>
@@ -58186,9 +58088,7 @@
         <v>After the change, EHS team confirm whether there is any problem or not as intial management.
 (Safety manager)</v>
       </c>
-      <c r="J34" s="62" t="s">
-        <v>651</v>
-      </c>
+      <c r="J34" s="62"/>
     </row>
     <row r="35" spans="3:10" ht="33">
       <c r="C35" s="550"/>
@@ -58211,9 +58111,7 @@
         <v>There is no IIP for Safety.
 (Safety Manager)</v>
       </c>
-      <c r="J35" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" spans="3:10" ht="49.5">
       <c r="C36" s="550"/>
@@ -58233,9 +58131,7 @@
 Or, the plan is approved by plant manager and issued in plant, but it was deployed not all department.
 (Safety Manager)</v>
       </c>
-      <c r="J36" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J36" s="12"/>
     </row>
     <row r="37" spans="3:10" ht="49.5">
       <c r="C37" s="550"/>
@@ -58254,9 +58150,7 @@
         <v>Safety IIP is approved by plant manager and safety committee, and it was deployed into all department.
 (Safety Manager)</v>
       </c>
-      <c r="J37" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J37" s="12"/>
     </row>
     <row r="38" spans="3:10" ht="33">
       <c r="C38" s="550" t="s">
@@ -58283,9 +58177,7 @@
         <v>There is a EHS manager.
 (Safety manager)</v>
       </c>
-      <c r="J38" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J38" s="12"/>
     </row>
     <row r="39" spans="3:10" ht="33">
       <c r="C39" s="550"/>
@@ -58304,9 +58196,7 @@
         <v>There is a EHS manager but he/she has multiple role.
 (Safety manager)</v>
       </c>
-      <c r="J39" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J39" s="12"/>
     </row>
     <row r="40" spans="3:10" ht="66">
       <c r="C40" s="550"/>
@@ -58326,9 +58216,7 @@
 And, a safety staff is asigned in plant.
 (Safety Manager)</v>
       </c>
-      <c r="J40" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J40" s="12"/>
     </row>
     <row r="41" spans="3:10" ht="66">
       <c r="C41" s="550"/>
@@ -58348,9 +58236,7 @@
 And, a safety staff's role also exclusive duty.
 (Safety Manager)</v>
       </c>
-      <c r="J41" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J41" s="12"/>
     </row>
     <row r="42" spans="3:10" ht="66">
       <c r="C42" s="550"/>
@@ -58370,9 +58256,7 @@
 And, his/her experiece is more than three years.
 (Safety Manager)</v>
       </c>
-      <c r="J42" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J42" s="12"/>
     </row>
     <row r="43" spans="3:10" ht="33">
       <c r="C43" s="550"/>
@@ -58393,9 +58277,7 @@
         <v>There is no Safety Engineer (SE).
 (Safety Manager)</v>
       </c>
-      <c r="J43" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J43" s="12"/>
     </row>
     <row r="44" spans="3:10" ht="33">
       <c r="C44" s="550"/>
@@ -58414,9 +58296,7 @@
         <v>SE has multiple roles.
 (Safety Manager)</v>
       </c>
-      <c r="J44" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J44" s="12"/>
     </row>
     <row r="45" spans="3:10" ht="33">
       <c r="C45" s="550"/>
@@ -58435,9 +58315,7 @@
         <v>There is a SE exclusive staff.
 (Safety Manager)</v>
       </c>
-      <c r="J45" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J45" s="12"/>
     </row>
     <row r="46" spans="3:10" ht="33">
       <c r="C46" s="550"/>
@@ -58456,9 +58334,7 @@
         <v>SE has a official license certified by government.
 (Safety Manager)</v>
       </c>
-      <c r="J46" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J46" s="12"/>
     </row>
     <row r="47" spans="3:10" ht="33">
       <c r="C47" s="550"/>
@@ -58477,9 +58353,7 @@
         <v xml:space="preserve">There are SEs (two or more), and they do not have multiple role.
 (Safety Manager) </v>
       </c>
-      <c r="J47" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J47" s="12"/>
     </row>
     <row r="48" spans="3:10" ht="16.5">
       <c r="C48" s="2"/>
@@ -58881,9 +58755,7 @@
         <v>There are documented OH&amp;S action plans and evidence of OH&amp;S results tracking.
 (System: Plant Manager: No.10)</v>
       </c>
-      <c r="J10" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" spans="2:10" ht="66">
       <c r="C11" s="550"/>
@@ -58903,9 +58775,7 @@
 To solve issues on H&amp;S, site leadership follow safety KPIs, and give directions to review the safety program if necessary.
 (Leadership: Plant Manager: No.6)</v>
       </c>
-      <c r="J11" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J11" s="29"/>
     </row>
     <row r="12" spans="2:10" ht="82.5">
       <c r="C12" s="550"/>
@@ -58925,9 +58795,7 @@
 Site leadership follow not only lagging indicator(e.g. # of injuries), but also leading indicators, and give directions to review and/or improve safety programs if necessary.
 (Leadership: Plant Manager: No.14)</v>
       </c>
-      <c r="J12" s="29" t="s">
-        <v>654</v>
-      </c>
+      <c r="J12" s="29"/>
     </row>
     <row r="13" spans="2:10" ht="82.5">
       <c r="C13" s="550"/>
@@ -58947,9 +58815,7 @@
 And, the strategy has been reviewed quarterly - its progress, validity. Also, revision/instruction for the starategy result have been implemented by plant manager.
 (Leadership: Plant manager: No.21)</v>
       </c>
-      <c r="J13" s="29" t="s">
-        <v>654</v>
-      </c>
+      <c r="J13" s="29"/>
     </row>
     <row r="14" spans="2:10" ht="66">
       <c r="C14" s="550" t="s">
@@ -58977,9 +58843,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:10" ht="82.5">
       <c r="C15" s="550"/>
@@ -59000,9 +58864,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:10" ht="49.5">
       <c r="C16" s="550"/>
@@ -59024,9 +58886,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" spans="3:10" ht="66">
       <c r="C17" s="550"/>
@@ -59046,9 +58906,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J17" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" spans="3:10" ht="49.5">
       <c r="C18" s="550"/>
@@ -59068,9 +58926,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J18" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J18" s="12"/>
     </row>
     <row r="19" spans="3:10" ht="49.5">
       <c r="C19" s="550"/>
@@ -59090,9 +58946,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" spans="3:10" ht="66">
       <c r="C20" s="550"/>
@@ -59113,9 +58967,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" spans="3:10" ht="49.5">
       <c r="C21" s="550"/>
@@ -59137,9 +58989,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J21" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J21" s="12"/>
     </row>
     <row r="22" spans="3:10" ht="49.5">
       <c r="C22" s="550"/>
@@ -59159,9 +59009,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J22" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" spans="3:10" ht="66">
       <c r="C23" s="550"/>
@@ -59182,9 +59030,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J23" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" spans="3:10" ht="82.5">
       <c r="C24" s="550"/>
@@ -59205,9 +59051,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J24" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J24" s="12"/>
     </row>
     <row r="25" spans="3:10" ht="66">
       <c r="C25" s="550"/>
@@ -59227,9 +59071,7 @@
 (Manager, SV)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J25" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" spans="3:10" ht="66">
       <c r="C26" s="550"/>
@@ -59251,9 +59093,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J26" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" spans="3:10" ht="66">
       <c r="C27" s="550"/>
@@ -59273,9 +59113,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J27" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" spans="3:10" ht="82.5">
       <c r="C28" s="550"/>
@@ -59295,9 +59133,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" spans="3:10" ht="93" customHeight="1">
       <c r="C29" s="550"/>
@@ -59317,9 +59153,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J29" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" spans="3:10" ht="93" customHeight="1">
       <c r="C30" s="550"/>
@@ -59339,9 +59173,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J30" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" spans="3:10" ht="66">
       <c r="C31" s="550" t="s">
@@ -59369,9 +59201,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J31" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" spans="3:10" ht="49.5">
       <c r="C32" s="550"/>
@@ -59390,9 +59220,7 @@
         <v>There is a lack of budget for either recurrence prevention, RA countermeasure, and working hours(human resource).
 (Safety Manager)</v>
       </c>
-      <c r="J32" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" spans="3:10" ht="66">
       <c r="C33" s="550"/>
@@ -59412,9 +59240,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J33" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" spans="3:10" ht="66">
       <c r="C34" s="550"/>
@@ -59434,9 +59260,7 @@
 (Safety Manager)
  *Ask Manager (not safety)</v>
       </c>
-      <c r="J34" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J34" s="12"/>
     </row>
     <row r="35" spans="3:10" ht="66">
       <c r="C35" s="550"/>
@@ -59455,9 +59279,7 @@
         <v>Budget is prepared even for sudden accidents. Or, in case of sudden accidents, additional budget is obtained, and recurrence prevention, RA countermeasure, and any other activities are implemented ahead of schedule.
 (Safety Manager)</v>
       </c>
-      <c r="J35" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J35" s="12"/>
     </row>
     <row r="36" spans="3:10" ht="16.5">
       <c r="C36" s="2"/>
@@ -59718,9 +59540,7 @@
 (System: Safety Manager: No.30)
  *Ask SVs</v>
       </c>
-      <c r="J4" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="2:10" ht="49.5">
       <c r="B5" s="2"/>
@@ -59740,9 +59560,7 @@
         <v>The safety manager can explain what actions are required for recurrence prevention when occuring a safety accicdent.
 (System: Safety Manager: No.86)</v>
       </c>
-      <c r="J5" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J5" s="59"/>
     </row>
     <row r="6" spans="2:10" ht="66">
       <c r="B6" s="2"/>
@@ -59762,9 +59580,7 @@
         <v>The safety leader can explain how such reviews are completed and why that method(s) is effective, providing feedback to SBU and assisting in determining countermeasures. (Example: Share more valid safety measreus than measures proposed by GBS/SBU)
 (System: Safety Manager: No.140)</v>
       </c>
-      <c r="J6" s="59" t="s">
-        <v>654</v>
-      </c>
+      <c r="J6" s="59"/>
     </row>
     <row r="7" spans="2:10" ht="49.5">
       <c r="C7" s="550"/>
@@ -59786,9 +59602,7 @@
  *At least, need to check its progress within 1 year.
 (Safety Manager)</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:10" ht="33">
       <c r="C8" s="550" t="s">
@@ -59815,9 +59629,7 @@
         <v>There is evidence that the required risk assessments have been done or there is a plan to complete.
 (System: Safety Manager: No.28)</v>
       </c>
-      <c r="J8" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J8" s="59"/>
     </row>
     <row r="9" spans="2:10" ht="33">
       <c r="C9" s="550"/>
@@ -59836,9 +59648,7 @@
         <v>There is a risk tracking that lists specific risks on site.
 (System: Safety Manager: No.53)</v>
       </c>
-      <c r="J9" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" spans="2:10" ht="49.5">
       <c r="C10" s="550"/>
@@ -59857,9 +59667,7 @@
         <v>There is at least one control prescribed for each risk identified. These controls are either administrative or technical by nature. The remaining risks are written in the work standard.
 (System: Safety Manager: No.85)</v>
       </c>
-      <c r="J10" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J10" s="59"/>
     </row>
     <row r="11" spans="2:10" ht="49.5">
       <c r="C11" s="550"/>
@@ -59878,9 +59686,7 @@
         <v>The respondent can show evidence of at least one review performed in the past 12 months where the risk assessment result/process was improved based on external best practice. 
 (System: Safety Manager: No.139)</v>
       </c>
-      <c r="J11" s="59" t="s">
-        <v>651</v>
-      </c>
+      <c r="J11" s="59"/>
     </row>
     <row r="12" spans="2:10" ht="33">
       <c r="C12" s="550"/>
@@ -59901,9 +59707,7 @@
         <v>There is a plan for Machine RA.
 (Safety Manager)</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J12" s="12"/>
     </row>
     <row r="13" spans="2:10" ht="49.5">
       <c r="C13" s="550"/>
@@ -59923,9 +59727,7 @@
  *No corrective plan for the delay.
 (Safety Manager)</v>
       </c>
-      <c r="J13" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J13" s="12"/>
     </row>
     <row r="14" spans="2:10" ht="49.5">
       <c r="C14" s="550"/>
@@ -59945,9 +59747,7 @@
 Or, there is a delay but corrective plan has been made for it, and it is on-going.
 (Safety Manager)</v>
       </c>
-      <c r="J14" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:10" ht="33">
       <c r="C15" s="550"/>
@@ -59966,9 +59766,7 @@
         <v>There is a plan for hardware contermeasures, and progressing ahead of the plan, but not yet completed.
 (Safety Manager)</v>
       </c>
-      <c r="J15" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J15" s="12"/>
     </row>
     <row r="16" spans="2:10" ht="49.5">
       <c r="C16" s="550"/>
@@ -59988,9 +59786,7 @@
  *all risks that could be countered by hardware have been reduced by hardware.
 (Safety Manager)</v>
       </c>
-      <c r="J16" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J16" s="12"/>
     </row>
     <row r="17" spans="3:10" ht="33">
       <c r="C17" s="550"/>
@@ -60011,9 +59807,7 @@
         <v>There is a plan for Task RA.
 (Safety Manager)</v>
       </c>
-      <c r="J17" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" spans="3:10" ht="49.5">
       <c r="C18" s="550"/>
@@ -60033,9 +59827,7 @@
  *No corrective plan for the delay.
 (Safety Manager)</v>
       </c>
-      <c r="J18" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J18" s="12"/>
     </row>
     <row r="19" spans="3:10" ht="49.5">
       <c r="C19" s="550"/>
@@ -60055,9 +59847,7 @@
 Or, there is a delay but corrective plan has been made for it, and it is on-going.
 (Safety Manager)</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J19" s="12"/>
     </row>
     <row r="20" spans="3:10" ht="33">
       <c r="C20" s="550"/>
@@ -60076,9 +59866,7 @@
         <v>There is a plan for Task RA, and progressing ahead of the plan, but not yet completed.
 (Safety Manager)</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J20" s="12"/>
     </row>
     <row r="21" spans="3:10" ht="33">
       <c r="C21" s="550"/>
@@ -60097,9 +59885,7 @@
         <v>All task RA have been completed.
 (Safety Manager)</v>
       </c>
-      <c r="J21" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J21" s="12"/>
     </row>
     <row r="22" spans="3:10" ht="33">
       <c r="C22" s="550"/>
@@ -60120,9 +59906,7 @@
         <v>SVs can explain what operation needs LOTO in their own process, and SOP has been already prepared.
 (SVs)</v>
       </c>
-      <c r="J22" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J22" s="12"/>
     </row>
     <row r="23" spans="3:10" ht="66">
       <c r="C23" s="550"/>
@@ -60142,9 +59926,7 @@
  In case of instruction is needed, they could instruct it.
 (SVs)</v>
       </c>
-      <c r="J23" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J23" s="12"/>
     </row>
     <row r="24" spans="3:10" ht="33">
       <c r="C24" s="550"/>
@@ -60165,9 +59947,7 @@
         <v>Safety trainings have been given to workers when new hired and/or trasfered. 
 (SVs)</v>
       </c>
-      <c r="J24" s="53" t="s">
-        <v>651</v>
-      </c>
+      <c r="J24" s="53"/>
     </row>
     <row r="25" spans="3:10" ht="33">
       <c r="C25" s="550"/>
@@ -60186,9 +59966,7 @@
         <v>Safety training meets regional legal requirement.
 (SVs)</v>
       </c>
-      <c r="J25" s="53" t="s">
-        <v>651</v>
-      </c>
+      <c r="J25" s="53"/>
     </row>
     <row r="26" spans="3:10" ht="33">
       <c r="C26" s="550"/>
@@ -60207,9 +59985,7 @@
         <v>Operators can work alone after their skill/knowledge is validated by the site's criteria.
 (SVs)</v>
       </c>
-      <c r="J26" s="53" t="s">
-        <v>651</v>
-      </c>
+      <c r="J26" s="53"/>
     </row>
     <row r="27" spans="3:10" ht="49.5">
       <c r="C27" s="550"/>
@@ -60229,9 +60005,7 @@
 Also, their skill/knowledge is followed up until they achieve 100%
 (SVs)</v>
       </c>
-      <c r="J27" s="53" t="s">
-        <v>651</v>
-      </c>
+      <c r="J27" s="53"/>
     </row>
     <row r="28" spans="3:10" ht="33">
       <c r="C28" s="550"/>
@@ -60250,9 +60024,7 @@
         <v>All operators understanding is confirmed periodically, and the confirmation step is standardized.
 (SVs)</v>
       </c>
-      <c r="J28" s="53" t="s">
-        <v>651</v>
-      </c>
+      <c r="J28" s="53"/>
     </row>
     <row r="29" spans="3:10" ht="33">
       <c r="C29" s="550" t="s">
@@ -60279,9 +60051,7 @@
         <v>OH&amp;S policy has been established at site. And the manager can explain it.
 (System: Plant Manager: No.9)</v>
       </c>
-      <c r="J29" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J29" s="29"/>
     </row>
     <row r="30" spans="3:10" ht="33">
       <c r="C30" s="550"/>
@@ -60300,9 +60070,7 @@
         <v>Management can describe and explain the site's OH&amp;S objectives and goals.
 (System: Manager: No.66)</v>
       </c>
-      <c r="J30" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J30" s="29"/>
     </row>
     <row r="31" spans="3:10" ht="33">
       <c r="C31" s="550"/>
@@ -60321,9 +60089,7 @@
         <v>The plan contains goals to be achieved which are relevant to the incidents and risks identified by the SBU.
 (System: Manager: No.98)</v>
       </c>
-      <c r="J31" s="59" t="s">
-        <v>654</v>
-      </c>
+      <c r="J31" s="59"/>
     </row>
     <row r="32" spans="3:10" ht="49.5">
       <c r="C32" s="550" t="s">
@@ -60350,9 +60116,7 @@
         <v>There is an officially appointed 3S leader on site. There is evidence of 3S inspections and recommended actions to improve 3S. 
 (System: Safety Manager: No.44+45)</v>
       </c>
-      <c r="J32" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J32" s="24"/>
     </row>
     <row r="33" spans="3:10" ht="33">
       <c r="C33" s="550"/>
@@ -60396,9 +60160,7 @@
 (Safety Manager)
 　*Ask SVs</v>
       </c>
-      <c r="J34" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J34" s="29"/>
     </row>
     <row r="35" spans="3:10" ht="33">
       <c r="C35" s="550"/>
@@ -60417,9 +60179,7 @@
         <v>There is evidence of a defined KY process that been communicated with all staff at least once in the past year.
 (System: Manager: No.26)</v>
       </c>
-      <c r="J35" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J35" s="29"/>
     </row>
     <row r="36" spans="3:10" ht="33">
       <c r="C36" s="550"/>
@@ -60438,9 +60198,7 @@
         <v>There is an officially appointed KY leader and KY representatives on site.
 (System: Manager: No.55)</v>
       </c>
-      <c r="J36" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J36" s="29"/>
     </row>
     <row r="37" spans="3:10" ht="66">
       <c r="C37" s="550"/>
@@ -60460,9 +60218,7 @@
 KYT records indicate that KYT is completed periodically in accordance with SBU and/or site standard by everyone on site. 
 (System: Safety Manager: No.83+112)</v>
       </c>
-      <c r="J37" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J37" s="29"/>
     </row>
     <row r="38" spans="3:10" ht="33">
       <c r="C38" s="550"/>
@@ -60481,9 +60237,7 @@
         <v>The KYT activity is evaluated and opportunity for inprovement is discussed with the plant manager annually. 
 (System: Safety Manager: No.113)</v>
       </c>
-      <c r="J38" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J38" s="29"/>
     </row>
     <row r="39" spans="3:10" ht="33">
       <c r="C39" s="550"/>
@@ -60504,9 +60258,7 @@
         <v>The respondent can clearly indicate how Site Safety Rules are reviewed and improved.
 (System: Safety Manager: No.41)</v>
       </c>
-      <c r="J39" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J39" s="29"/>
     </row>
     <row r="40" spans="3:10" ht="49.5">
       <c r="C40" s="550"/>
@@ -60525,9 +60277,7 @@
         <v>Line-management conducts floor observations(e.g. site tours) and provide feedbacks to teammates to ensure adherence to safety rules, such as procedures, standards, etc. 
 (Leadership: SVs: No.9)</v>
       </c>
-      <c r="J40" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J40" s="24"/>
     </row>
     <row r="41" spans="3:10" ht="16.5">
       <c r="C41" s="2"/>

--- a/export_templates/dp_solid_checksheet.xlsx
+++ b/export_templates/dp_solid_checksheet.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://salesbridge-my.sharepoint.com/personal/thanida_wanamkang_bridgestone_com/Documents/Desktop/Cont. 2026/01. Current Task/02. Audit/03. Solidification Assessment/"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="40" documentId="8_{26C65EE9-CF1B-4EBE-AF0B-BC19160CFA59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A33E1C6-3611-4971-9B8A-A2F94DE901C4}"/>
   <bookViews>
@@ -10662,7 +10660,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10719,7 +10717,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11162,19 +11160,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -12098,19 +12096,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12544,19 +12542,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12851,13 +12849,13 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13160,19 +13158,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13489,19 +13487,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -14082,19 +14080,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14371,7 +14369,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14444,7 +14442,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14517,7 +14515,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14590,7 +14588,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14875,7 +14873,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14932,7 +14930,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15231,7 +15229,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15288,7 +15286,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15605,13 +15603,13 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16092,19 +16090,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -17028,19 +17026,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17474,19 +17472,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17785,13 +17783,13 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>

--- a/export_templates/dp_solid_checksheet.xlsx
+++ b/export_templates/dp_solid_checksheet.xlsx
@@ -30173,9 +30173,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:25">
-      <c r="X1" s="85" t="s">
-        <v>0</v>
-      </c>
+      <c r="X1" s="85"/>
     </row>
     <row r="2" spans="2:25" ht="18" customHeight="1">
       <c r="B2" s="86"/>
@@ -30198,9 +30196,7 @@
       <c r="T2" s="400"/>
       <c r="U2" s="400"/>
       <c r="V2" s="400"/>
-      <c r="W2" s="443">
-        <v>7310</v>
-      </c>
+      <c r="W2" s="443"/>
       <c r="X2" s="443"/>
     </row>
     <row r="3" spans="2:25" ht="61" customHeight="1">
@@ -30234,9 +30230,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="444"/>
-      <c r="D4" s="444" t="s">
-        <v>3</v>
-      </c>
+      <c r="D4" s="444"/>
       <c r="E4" s="444"/>
       <c r="F4" s="444"/>
       <c r="G4" s="444" t="s">
@@ -30244,9 +30238,7 @@
       </c>
       <c r="H4" s="444"/>
       <c r="I4" s="444"/>
-      <c r="J4" s="445" t="s">
-        <v>5</v>
-      </c>
+      <c r="J4" s="445"/>
       <c r="K4" s="445"/>
       <c r="L4" s="445"/>
       <c r="M4" s="445"/>
@@ -32525,9 +32517,7 @@
         <v>Autonomously KY has been conducted but it is conducted by group. (not individual)
 (Operator)</v>
       </c>
-      <c r="J19" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J19" s="12"/>
       <c r="K19" s="141"/>
       <c r="L19" s="141"/>
       <c r="M19" s="141"/>
@@ -32554,9 +32544,7 @@
 (need to check evidence)
 (Operator)</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J20" s="12"/>
       <c r="K20" s="141"/>
       <c r="L20" s="141"/>
       <c r="M20" s="141"/>
@@ -32579,9 +32567,7 @@
         <v>SVs or leaders conduct GENBA patrol to confirm autonomously KY result, and instruct teammates if needed.
 (Operator)</v>
       </c>
-      <c r="J21" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J21" s="12"/>
       <c r="K21" s="141"/>
       <c r="L21" s="141"/>
       <c r="M21" s="141"/>
@@ -32610,9 +32596,7 @@
  *if the site has the system to manage bottom up KAIZEN cycle as from KY activity, this item could be judged "Yes"
 (Operator)</v>
       </c>
-      <c r="J22" s="12" t="s">
-        <v>654</v>
-      </c>
+      <c r="J22" s="12"/>
       <c r="K22" s="141"/>
       <c r="L22" s="141"/>
       <c r="M22" s="141"/>
@@ -39876,88 +39860,40 @@
       <c r="B4" s="57"/>
       <c r="C4" s="57"/>
       <c r="D4" s="57"/>
-      <c r="E4" s="65" t="s">
-        <v>710</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>711</v>
-      </c>
-      <c r="G4" s="65" t="s">
-        <v>712</v>
-      </c>
-      <c r="H4" s="65" t="s">
-        <v>713</v>
-      </c>
-      <c r="I4" s="65" t="s">
-        <v>714</v>
-      </c>
-      <c r="J4" s="65" t="s">
-        <v>715</v>
-      </c>
-      <c r="K4" s="65" t="s">
-        <v>716</v>
-      </c>
-      <c r="L4" s="65" t="s">
-        <v>717</v>
-      </c>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
       <c r="M4" s="65" t="s">
         <v>718</v>
       </c>
       <c r="P4" s="57"/>
       <c r="Q4" s="57"/>
       <c r="R4" s="57"/>
-      <c r="S4" s="65" t="s">
-        <v>710</v>
-      </c>
-      <c r="T4" s="65" t="s">
-        <v>711</v>
-      </c>
-      <c r="U4" s="65" t="s">
-        <v>712</v>
-      </c>
-      <c r="V4" s="65" t="s">
-        <v>713</v>
-      </c>
-      <c r="W4" s="65" t="s">
-        <v>714</v>
-      </c>
-      <c r="X4" s="65" t="s">
-        <v>715</v>
-      </c>
-      <c r="Y4" s="65" t="s">
-        <v>716</v>
-      </c>
-      <c r="Z4" s="65" t="s">
-        <v>717</v>
-      </c>
+      <c r="S4" s="65"/>
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65"/>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
       <c r="AA4" s="65" t="s">
         <v>718</v>
       </c>
       <c r="AK4" s="57"/>
-      <c r="AL4" s="65" t="s">
-        <v>710</v>
-      </c>
-      <c r="AM4" s="65" t="s">
-        <v>711</v>
-      </c>
-      <c r="AN4" s="65" t="s">
-        <v>712</v>
-      </c>
-      <c r="AO4" s="65" t="s">
-        <v>713</v>
-      </c>
-      <c r="AP4" s="65" t="s">
-        <v>714</v>
-      </c>
-      <c r="AQ4" s="65" t="s">
-        <v>715</v>
-      </c>
-      <c r="AR4" s="65" t="s">
-        <v>716</v>
-      </c>
-      <c r="AS4" s="65" t="s">
-        <v>717</v>
-      </c>
+      <c r="AL4" s="65"/>
+      <c r="AM4" s="65"/>
+      <c r="AN4" s="65"/>
+      <c r="AO4" s="65"/>
+      <c r="AP4" s="65"/>
+      <c r="AQ4" s="65"/>
+      <c r="AR4" s="65"/>
+      <c r="AS4" s="65"/>
       <c r="AT4" s="65" t="s">
         <v>718</v>
       </c>
@@ -39972,33 +39908,15 @@
       <c r="D5" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E5" s="57">
-        <v>4</v>
-      </c>
-      <c r="F5" s="57">
-        <v>5</v>
-      </c>
-      <c r="G5" s="57">
-        <v>5</v>
-      </c>
-      <c r="H5" s="57">
-        <v>3</v>
-      </c>
-      <c r="I5" s="57">
-        <v>1</v>
-      </c>
-      <c r="J5" s="57">
-        <v>5</v>
-      </c>
-      <c r="K5" s="57">
-        <v>5</v>
-      </c>
-      <c r="L5" s="57">
-        <v>5</v>
-      </c>
-      <c r="M5" s="57">
-        <v>5</v>
-      </c>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
       <c r="P5" s="57" t="s">
         <v>719</v>
       </c>
@@ -40092,33 +40010,15 @@
       <c r="D6" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E6" s="57">
-        <v>5</v>
-      </c>
-      <c r="F6" s="57">
-        <v>1</v>
-      </c>
-      <c r="G6" s="57">
-        <v>5</v>
-      </c>
-      <c r="H6" s="57">
-        <v>5</v>
-      </c>
-      <c r="I6" s="57">
-        <v>5</v>
-      </c>
-      <c r="J6" s="57">
-        <v>5</v>
-      </c>
-      <c r="K6" s="57">
-        <v>5</v>
-      </c>
-      <c r="L6" s="57">
-        <v>4</v>
-      </c>
-      <c r="M6" s="57">
-        <v>1</v>
-      </c>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
       <c r="P6" s="57"/>
       <c r="Q6" s="59" t="s">
         <v>64</v>
@@ -40210,33 +40110,15 @@
       <c r="D7" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E7" s="57">
-        <v>4</v>
-      </c>
-      <c r="F7" s="57">
-        <v>5</v>
-      </c>
-      <c r="G7" s="57">
-        <v>5</v>
-      </c>
-      <c r="H7" s="57">
-        <v>3</v>
-      </c>
-      <c r="I7" s="57">
-        <v>5</v>
-      </c>
-      <c r="J7" s="57">
-        <v>5</v>
-      </c>
-      <c r="K7" s="57">
-        <v>4</v>
-      </c>
-      <c r="L7" s="57">
-        <v>5</v>
-      </c>
-      <c r="M7" s="57">
-        <v>5</v>
-      </c>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57"/>
       <c r="P7" s="57"/>
       <c r="Q7" s="59" t="s">
         <v>70</v>
@@ -40330,33 +40212,15 @@
       <c r="D8" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E8" s="57">
-        <v>5</v>
-      </c>
-      <c r="F8" s="57">
-        <v>5</v>
-      </c>
-      <c r="G8" s="57">
-        <v>5</v>
-      </c>
-      <c r="H8" s="57">
-        <v>3</v>
-      </c>
-      <c r="I8" s="57">
-        <v>5</v>
-      </c>
-      <c r="J8" s="57">
-        <v>5</v>
-      </c>
-      <c r="K8" s="57">
-        <v>3</v>
-      </c>
-      <c r="L8" s="57">
-        <v>5</v>
-      </c>
-      <c r="M8" s="57">
-        <v>5</v>
-      </c>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
       <c r="P8" s="57" t="s">
         <v>720</v>
       </c>
@@ -40450,33 +40314,15 @@
       <c r="D9" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E9" s="57">
-        <v>3</v>
-      </c>
-      <c r="F9" s="57">
-        <v>4</v>
-      </c>
-      <c r="G9" s="57">
-        <v>4</v>
-      </c>
-      <c r="H9" s="57">
-        <v>1</v>
-      </c>
-      <c r="I9" s="57">
-        <v>2</v>
-      </c>
-      <c r="J9" s="57">
-        <v>5</v>
-      </c>
-      <c r="K9" s="57">
-        <v>2</v>
-      </c>
-      <c r="L9" s="57">
-        <v>1</v>
-      </c>
-      <c r="M9" s="57">
-        <v>5</v>
-      </c>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
       <c r="P9" s="57"/>
       <c r="Q9" s="59" t="s">
         <v>80</v>
@@ -40568,33 +40414,15 @@
       <c r="D10" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E10" s="57">
-        <v>3</v>
-      </c>
-      <c r="F10" s="57">
-        <v>1</v>
-      </c>
-      <c r="G10" s="57">
-        <v>5</v>
-      </c>
-      <c r="H10" s="57">
-        <v>3</v>
-      </c>
-      <c r="I10" s="57">
-        <v>5</v>
-      </c>
-      <c r="J10" s="57">
-        <v>5</v>
-      </c>
-      <c r="K10" s="57">
-        <v>3</v>
-      </c>
-      <c r="L10" s="57">
-        <v>1</v>
-      </c>
-      <c r="M10" s="57">
-        <v>3</v>
-      </c>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
       <c r="P10" s="57"/>
       <c r="Q10" s="59" t="s">
         <v>83</v>
@@ -40686,33 +40514,15 @@
       <c r="D11" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E11" s="57">
-        <v>3</v>
-      </c>
-      <c r="F11" s="57">
-        <v>1</v>
-      </c>
-      <c r="G11" s="57">
-        <v>3</v>
-      </c>
-      <c r="H11" s="57">
-        <v>1</v>
-      </c>
-      <c r="I11" s="57">
-        <v>3</v>
-      </c>
-      <c r="J11" s="57">
-        <v>5</v>
-      </c>
-      <c r="K11" s="57">
-        <v>3</v>
-      </c>
-      <c r="L11" s="57">
-        <v>1</v>
-      </c>
-      <c r="M11" s="57">
-        <v>5</v>
-      </c>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
       <c r="P11" s="57"/>
       <c r="Q11" s="59" t="s">
         <v>88</v>
@@ -40765,31 +40575,15 @@
       <c r="D12" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="E12" s="57">
-        <v>4</v>
-      </c>
-      <c r="F12" s="57">
-        <v>2</v>
-      </c>
-      <c r="G12" s="57">
-        <v>5</v>
-      </c>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
       <c r="H12" s="57"/>
-      <c r="I12" s="57">
-        <v>1</v>
-      </c>
-      <c r="J12" s="57">
-        <v>5</v>
-      </c>
-      <c r="K12" s="57">
-        <v>1</v>
-      </c>
-      <c r="L12" s="57">
-        <v>1</v>
-      </c>
-      <c r="M12" s="57">
-        <v>5</v>
-      </c>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
       <c r="P12" s="57"/>
       <c r="Q12" s="59" t="s">
         <v>93</v>
@@ -40899,33 +40693,17 @@
       <c r="D14" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="E14" s="57">
-        <v>1</v>
-      </c>
-      <c r="F14" s="57">
-        <v>5</v>
-      </c>
-      <c r="G14" s="57">
-        <v>5</v>
-      </c>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
       <c r="H14" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="I14" s="57">
-        <v>1</v>
-      </c>
-      <c r="J14" s="57">
-        <v>5</v>
-      </c>
-      <c r="K14" s="57">
-        <v>1</v>
-      </c>
-      <c r="L14" s="57">
-        <v>2</v>
-      </c>
-      <c r="M14" s="57">
-        <v>5</v>
-      </c>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
       <c r="P14" s="57"/>
       <c r="Q14" s="59" t="s">
         <v>98</v>
@@ -40970,30 +40748,14 @@
         <v>A</v>
       </c>
       <c r="AK14" s="57"/>
-      <c r="AL14" s="65" t="s">
-        <v>710</v>
-      </c>
-      <c r="AM14" s="65" t="s">
-        <v>711</v>
-      </c>
-      <c r="AN14" s="65" t="s">
-        <v>712</v>
-      </c>
-      <c r="AO14" s="65" t="s">
-        <v>713</v>
-      </c>
-      <c r="AP14" s="65" t="s">
-        <v>714</v>
-      </c>
-      <c r="AQ14" s="65" t="s">
-        <v>715</v>
-      </c>
-      <c r="AR14" s="65" t="s">
-        <v>716</v>
-      </c>
-      <c r="AS14" s="65" t="s">
-        <v>717</v>
-      </c>
+      <c r="AL14" s="65"/>
+      <c r="AM14" s="65"/>
+      <c r="AN14" s="65"/>
+      <c r="AO14" s="65"/>
+      <c r="AP14" s="65"/>
+      <c r="AQ14" s="65"/>
+      <c r="AR14" s="65"/>
+      <c r="AS14" s="65"/>
       <c r="AT14" s="65" t="s">
         <v>718</v>
       </c>
@@ -41008,33 +40770,15 @@
       <c r="D15" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E15" s="57">
-        <v>3</v>
-      </c>
-      <c r="F15" s="57">
-        <v>4</v>
-      </c>
-      <c r="G15" s="57">
-        <v>1</v>
-      </c>
-      <c r="H15" s="57">
-        <v>1</v>
-      </c>
-      <c r="I15" s="57">
-        <v>4</v>
-      </c>
-      <c r="J15" s="57">
-        <v>1</v>
-      </c>
-      <c r="K15" s="57">
-        <v>5</v>
-      </c>
-      <c r="L15" s="57">
-        <v>3</v>
-      </c>
-      <c r="M15" s="57">
-        <v>5</v>
-      </c>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
       <c r="P15" s="57" t="s">
         <v>721</v>
       </c>
@@ -41128,33 +40872,15 @@
       <c r="D16" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E16" s="57">
-        <v>4</v>
-      </c>
-      <c r="F16" s="57">
-        <v>4</v>
-      </c>
-      <c r="G16" s="57">
-        <v>4</v>
-      </c>
-      <c r="H16" s="57">
-        <v>4</v>
-      </c>
-      <c r="I16" s="57">
-        <v>3</v>
-      </c>
-      <c r="J16" s="57">
-        <v>4</v>
-      </c>
-      <c r="K16" s="57">
-        <v>3</v>
-      </c>
-      <c r="L16" s="57">
-        <v>4</v>
-      </c>
-      <c r="M16" s="57">
-        <v>5</v>
-      </c>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
       <c r="P16" s="57"/>
       <c r="Q16" s="59" t="s">
         <v>109</v>
@@ -41246,33 +40972,15 @@
       <c r="D17" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E17" s="57">
-        <v>5</v>
-      </c>
-      <c r="F17" s="57">
-        <v>5</v>
-      </c>
-      <c r="G17" s="57">
-        <v>5</v>
-      </c>
-      <c r="H17" s="57">
-        <v>1</v>
-      </c>
-      <c r="I17" s="57">
-        <v>3</v>
-      </c>
-      <c r="J17" s="57">
-        <v>5</v>
-      </c>
-      <c r="K17" s="57">
-        <v>4</v>
-      </c>
-      <c r="L17" s="57">
-        <v>5</v>
-      </c>
-      <c r="M17" s="57">
-        <v>5</v>
-      </c>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
       <c r="P17" s="57"/>
       <c r="Q17" s="59" t="s">
         <v>114</v>
@@ -41447,33 +41155,15 @@
       <c r="D19" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E19" s="57">
-        <v>4</v>
-      </c>
-      <c r="F19" s="57">
-        <v>4</v>
-      </c>
-      <c r="G19" s="57">
-        <v>5</v>
-      </c>
-      <c r="H19" s="57">
-        <v>1</v>
-      </c>
-      <c r="I19" s="57">
-        <v>3</v>
-      </c>
-      <c r="J19" s="57">
-        <v>5</v>
-      </c>
-      <c r="K19" s="57">
-        <v>1</v>
-      </c>
-      <c r="L19" s="57">
-        <v>2</v>
-      </c>
-      <c r="M19" s="57">
-        <v>1</v>
-      </c>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
       <c r="P19" s="57"/>
       <c r="Q19" s="59" t="s">
         <v>125</v>
@@ -41526,33 +41216,15 @@
       <c r="D20" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="E20" s="57">
-        <v>4</v>
-      </c>
-      <c r="F20" s="57">
-        <v>5</v>
-      </c>
-      <c r="G20" s="57">
-        <v>4</v>
-      </c>
-      <c r="H20" s="57">
-        <v>4</v>
-      </c>
-      <c r="I20" s="57">
-        <v>4</v>
-      </c>
-      <c r="J20" s="57">
-        <v>4</v>
-      </c>
-      <c r="K20" s="57">
-        <v>2</v>
-      </c>
-      <c r="L20" s="57">
-        <v>4</v>
-      </c>
-      <c r="M20" s="57">
-        <v>3</v>
-      </c>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
       <c r="P20" s="57"/>
       <c r="Q20" s="59" t="s">
         <v>131</v>
@@ -41605,33 +41277,15 @@
       <c r="D21" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E21" s="57">
-        <v>4</v>
-      </c>
-      <c r="F21" s="57">
-        <v>3</v>
-      </c>
-      <c r="G21" s="57">
-        <v>3</v>
-      </c>
-      <c r="H21" s="57">
-        <v>1</v>
-      </c>
-      <c r="I21" s="57">
-        <v>3</v>
-      </c>
-      <c r="J21" s="57">
-        <v>5</v>
-      </c>
-      <c r="K21" s="57">
-        <v>1</v>
-      </c>
-      <c r="L21" s="57">
-        <v>3</v>
-      </c>
-      <c r="M21" s="57">
-        <v>5</v>
-      </c>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
       <c r="P21" s="57"/>
       <c r="Q21" s="59" t="s">
         <v>134</v>
@@ -41684,33 +41338,15 @@
       <c r="D22" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E22" s="57">
-        <v>2</v>
-      </c>
-      <c r="F22" s="57">
-        <v>3</v>
-      </c>
-      <c r="G22" s="57">
-        <v>5</v>
-      </c>
-      <c r="H22" s="57">
-        <v>3</v>
-      </c>
-      <c r="I22" s="57">
-        <v>3</v>
-      </c>
-      <c r="J22" s="57">
-        <v>3</v>
-      </c>
-      <c r="K22" s="57">
-        <v>1</v>
-      </c>
-      <c r="L22" s="57">
-        <v>2</v>
-      </c>
-      <c r="M22" s="57">
-        <v>5</v>
-      </c>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
       <c r="P22" s="57"/>
       <c r="Q22" s="59" t="s">
         <v>139</v>
@@ -41763,33 +41399,15 @@
       <c r="D23" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="E23" s="57">
-        <v>4</v>
-      </c>
-      <c r="F23" s="57">
-        <v>4</v>
-      </c>
-      <c r="G23" s="57">
-        <v>5</v>
-      </c>
-      <c r="H23" s="57">
-        <v>4</v>
-      </c>
-      <c r="I23" s="57">
-        <v>3</v>
-      </c>
-      <c r="J23" s="57">
-        <v>5</v>
-      </c>
-      <c r="K23" s="57">
-        <v>3</v>
-      </c>
-      <c r="L23" s="57">
-        <v>5</v>
-      </c>
-      <c r="M23" s="57">
-        <v>5</v>
-      </c>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
       <c r="P23" s="57"/>
       <c r="Q23" s="59" t="s">
         <v>144</v>
@@ -41921,33 +41539,15 @@
       <c r="D25" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E25" s="57">
-        <v>4</v>
-      </c>
-      <c r="F25" s="57">
-        <v>4</v>
-      </c>
-      <c r="G25" s="57">
-        <v>5</v>
-      </c>
-      <c r="H25" s="57">
-        <v>3</v>
-      </c>
-      <c r="I25" s="57">
-        <v>4</v>
-      </c>
-      <c r="J25" s="57">
-        <v>4</v>
-      </c>
-      <c r="K25" s="57">
-        <v>4</v>
-      </c>
-      <c r="L25" s="57">
-        <v>4</v>
-      </c>
-      <c r="M25" s="57">
-        <v>4</v>
-      </c>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
       <c r="P25" s="57"/>
       <c r="Q25" s="59" t="s">
         <v>152</v>
@@ -42000,33 +41600,15 @@
       <c r="D26" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E26" s="57">
-        <v>5</v>
-      </c>
-      <c r="F26" s="57">
-        <v>4</v>
-      </c>
-      <c r="G26" s="57">
-        <v>5</v>
-      </c>
-      <c r="H26" s="57">
-        <v>3</v>
-      </c>
-      <c r="I26" s="57">
-        <v>1</v>
-      </c>
-      <c r="J26" s="57">
-        <v>4</v>
-      </c>
-      <c r="K26" s="57">
-        <v>4</v>
-      </c>
-      <c r="L26" s="57">
-        <v>4</v>
-      </c>
-      <c r="M26" s="57">
-        <v>4</v>
-      </c>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
       <c r="P26" s="57"/>
       <c r="Q26" s="59" t="s">
         <v>157</v>
@@ -42079,33 +41661,15 @@
       <c r="D27" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E27" s="57">
-        <v>4</v>
-      </c>
-      <c r="F27" s="57">
-        <v>3</v>
-      </c>
-      <c r="G27" s="57">
-        <v>5</v>
-      </c>
-      <c r="H27" s="57">
-        <v>3</v>
-      </c>
-      <c r="I27" s="57">
-        <v>1</v>
-      </c>
-      <c r="J27" s="57">
-        <v>3</v>
-      </c>
-      <c r="K27" s="57">
-        <v>4</v>
-      </c>
-      <c r="L27" s="57">
-        <v>3</v>
-      </c>
-      <c r="M27" s="57">
-        <v>5</v>
-      </c>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
       <c r="P27" s="57"/>
       <c r="Q27" s="59" t="s">
         <v>162</v>
@@ -42158,33 +41722,15 @@
       <c r="D28" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E28" s="57">
-        <v>3</v>
-      </c>
-      <c r="F28" s="57">
-        <v>3</v>
-      </c>
-      <c r="G28" s="57">
-        <v>3</v>
-      </c>
-      <c r="H28" s="57">
-        <v>3</v>
-      </c>
-      <c r="I28" s="57">
-        <v>2</v>
-      </c>
-      <c r="J28" s="57">
-        <v>3</v>
-      </c>
-      <c r="K28" s="57">
-        <v>2</v>
-      </c>
-      <c r="L28" s="57">
-        <v>3</v>
-      </c>
-      <c r="M28" s="57">
-        <v>5</v>
-      </c>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
       <c r="P28" s="57"/>
       <c r="Q28" s="59" t="s">
         <v>167</v>
@@ -42239,33 +41785,15 @@
       <c r="D29" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E29" s="57">
-        <v>3</v>
-      </c>
-      <c r="F29" s="57">
-        <v>5</v>
-      </c>
-      <c r="G29" s="57">
-        <v>4</v>
-      </c>
-      <c r="H29" s="57">
-        <v>4</v>
-      </c>
-      <c r="I29" s="57">
-        <v>2</v>
-      </c>
-      <c r="J29" s="57">
-        <v>5</v>
-      </c>
-      <c r="K29" s="57">
-        <v>4</v>
-      </c>
-      <c r="L29" s="57">
-        <v>4</v>
-      </c>
-      <c r="M29" s="57">
-        <v>4</v>
-      </c>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
       <c r="P29" s="57" t="s">
         <v>723</v>
       </c>
@@ -42318,33 +41846,15 @@
       <c r="D30" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E30" s="57">
-        <v>3</v>
-      </c>
-      <c r="F30" s="57">
-        <v>5</v>
-      </c>
-      <c r="G30" s="57">
-        <v>4</v>
-      </c>
-      <c r="H30" s="57">
-        <v>3</v>
-      </c>
-      <c r="I30" s="57">
-        <v>2</v>
-      </c>
-      <c r="J30" s="57">
-        <v>5</v>
-      </c>
-      <c r="K30" s="57">
-        <v>3</v>
-      </c>
-      <c r="L30" s="57">
-        <v>5</v>
-      </c>
-      <c r="M30" s="57">
-        <v>4</v>
-      </c>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
       <c r="P30" s="57"/>
       <c r="Q30"/>
       <c r="R30" s="57" t="s">
@@ -42395,33 +41905,15 @@
       <c r="D31" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E31" s="57">
-        <v>4</v>
-      </c>
-      <c r="F31" s="57">
-        <v>1</v>
-      </c>
-      <c r="G31" s="57">
-        <v>2</v>
-      </c>
-      <c r="H31" s="57">
-        <v>1</v>
-      </c>
-      <c r="I31" s="57">
-        <v>1</v>
-      </c>
-      <c r="J31" s="57">
-        <v>2</v>
-      </c>
-      <c r="K31" s="57">
-        <v>1</v>
-      </c>
-      <c r="L31" s="57">
-        <v>1</v>
-      </c>
-      <c r="M31" s="57">
-        <v>3</v>
-      </c>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
       <c r="P31" s="57"/>
       <c r="Q31" s="59" t="s">
         <v>178</v>
@@ -42549,33 +42041,15 @@
       <c r="D33" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E33" s="57">
-        <v>5</v>
-      </c>
-      <c r="F33" s="57">
-        <v>4</v>
-      </c>
-      <c r="G33" s="57">
-        <v>4</v>
-      </c>
-      <c r="H33" s="57">
-        <v>2</v>
-      </c>
-      <c r="I33" s="57">
-        <v>5</v>
-      </c>
-      <c r="J33" s="57">
-        <v>5</v>
-      </c>
-      <c r="K33" s="57">
-        <v>4</v>
-      </c>
-      <c r="L33" s="57">
-        <v>4</v>
-      </c>
-      <c r="M33" s="57">
-        <v>5</v>
-      </c>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="57"/>
       <c r="P33" s="57"/>
       <c r="Q33" s="58" t="s">
         <v>184</v>
@@ -43051,88 +42525,40 @@
       <c r="B50" s="57"/>
       <c r="C50" s="57"/>
       <c r="D50" s="57"/>
-      <c r="E50" s="65" t="s">
-        <v>710</v>
-      </c>
-      <c r="F50" s="65" t="s">
-        <v>711</v>
-      </c>
-      <c r="G50" s="65" t="s">
-        <v>712</v>
-      </c>
-      <c r="H50" s="65" t="s">
-        <v>713</v>
-      </c>
-      <c r="I50" s="65" t="s">
-        <v>714</v>
-      </c>
-      <c r="J50" s="65" t="s">
-        <v>715</v>
-      </c>
-      <c r="K50" s="65" t="s">
-        <v>716</v>
-      </c>
-      <c r="L50" s="65" t="s">
-        <v>717</v>
-      </c>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="65"/>
+      <c r="I50" s="65"/>
+      <c r="J50" s="65"/>
+      <c r="K50" s="65"/>
+      <c r="L50" s="65"/>
       <c r="M50" s="65" t="s">
         <v>718</v>
       </c>
       <c r="P50" s="57"/>
       <c r="Q50" s="57"/>
       <c r="R50" s="57"/>
-      <c r="S50" s="65" t="s">
-        <v>710</v>
-      </c>
-      <c r="T50" s="65" t="s">
-        <v>711</v>
-      </c>
-      <c r="U50" s="65" t="s">
-        <v>712</v>
-      </c>
-      <c r="V50" s="65" t="s">
-        <v>713</v>
-      </c>
-      <c r="W50" s="65" t="s">
-        <v>714</v>
-      </c>
-      <c r="X50" s="65" t="s">
-        <v>715</v>
-      </c>
-      <c r="Y50" s="65" t="s">
-        <v>716</v>
-      </c>
-      <c r="Z50" s="65" t="s">
-        <v>717</v>
-      </c>
+      <c r="S50" s="65"/>
+      <c r="T50" s="65"/>
+      <c r="U50" s="65"/>
+      <c r="V50" s="65"/>
+      <c r="W50" s="65"/>
+      <c r="X50" s="65"/>
+      <c r="Y50" s="65"/>
+      <c r="Z50" s="65"/>
       <c r="AA50" s="65" t="s">
         <v>718</v>
       </c>
       <c r="AK50" s="57"/>
-      <c r="AL50" s="65" t="s">
-        <v>710</v>
-      </c>
-      <c r="AM50" s="65" t="s">
-        <v>711</v>
-      </c>
-      <c r="AN50" s="65" t="s">
-        <v>712</v>
-      </c>
-      <c r="AO50" s="65" t="s">
-        <v>713</v>
-      </c>
-      <c r="AP50" s="65" t="s">
-        <v>714</v>
-      </c>
-      <c r="AQ50" s="65" t="s">
-        <v>715</v>
-      </c>
-      <c r="AR50" s="65" t="s">
-        <v>716</v>
-      </c>
-      <c r="AS50" s="65" t="s">
-        <v>717</v>
-      </c>
+      <c r="AL50" s="65"/>
+      <c r="AM50" s="65"/>
+      <c r="AN50" s="65"/>
+      <c r="AO50" s="65"/>
+      <c r="AP50" s="65"/>
+      <c r="AQ50" s="65"/>
+      <c r="AR50" s="65"/>
+      <c r="AS50" s="65"/>
       <c r="AT50" s="65" t="s">
         <v>718</v>
       </c>
@@ -43147,33 +42573,15 @@
       <c r="D51" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E51" s="57">
-        <v>3</v>
-      </c>
-      <c r="F51" s="57">
-        <v>5</v>
-      </c>
-      <c r="G51" s="57">
-        <v>2</v>
-      </c>
-      <c r="H51" s="57">
-        <v>3</v>
-      </c>
-      <c r="I51" s="57">
-        <v>1</v>
-      </c>
-      <c r="J51" s="57">
-        <v>5</v>
-      </c>
-      <c r="K51" s="57">
-        <v>5</v>
-      </c>
-      <c r="L51" s="57">
-        <v>3</v>
-      </c>
-      <c r="M51" s="57">
-        <v>5</v>
-      </c>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
+      <c r="L51" s="57"/>
+      <c r="M51" s="57"/>
       <c r="P51" s="57" t="s">
         <v>719</v>
       </c>
@@ -43273,33 +42681,15 @@
       <c r="D52" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E52" s="57">
-        <v>5</v>
-      </c>
-      <c r="F52" s="57">
-        <v>1</v>
-      </c>
-      <c r="G52" s="57">
-        <v>5</v>
-      </c>
-      <c r="H52" s="57">
-        <v>5</v>
-      </c>
-      <c r="I52" s="57">
-        <v>3</v>
-      </c>
-      <c r="J52" s="57">
-        <v>5</v>
-      </c>
-      <c r="K52" s="57">
-        <v>5</v>
-      </c>
-      <c r="L52" s="57">
-        <v>4</v>
-      </c>
-      <c r="M52" s="57">
-        <v>1</v>
-      </c>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="57"/>
+      <c r="L52" s="57"/>
+      <c r="M52" s="57"/>
       <c r="P52" s="57"/>
       <c r="Q52" s="59" t="s">
         <v>240</v>
@@ -43397,33 +42787,15 @@
       <c r="D53" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E53" s="57">
-        <v>4</v>
-      </c>
-      <c r="F53" s="57">
-        <v>5</v>
-      </c>
-      <c r="G53" s="57">
-        <v>4</v>
-      </c>
-      <c r="H53" s="57">
-        <v>3</v>
-      </c>
-      <c r="I53" s="57">
-        <v>5</v>
-      </c>
-      <c r="J53" s="57">
-        <v>5</v>
-      </c>
-      <c r="K53" s="57">
-        <v>4</v>
-      </c>
-      <c r="L53" s="57">
-        <v>5</v>
-      </c>
-      <c r="M53" s="57">
-        <v>5</v>
-      </c>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="57"/>
+      <c r="L53" s="57"/>
+      <c r="M53" s="57"/>
       <c r="P53" s="57"/>
       <c r="Q53" s="58" t="s">
         <v>729</v>
@@ -43523,33 +42895,15 @@
       <c r="D54" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E54" s="57">
-        <v>5</v>
-      </c>
-      <c r="F54" s="57">
-        <v>3</v>
-      </c>
-      <c r="G54" s="57">
-        <v>5</v>
-      </c>
-      <c r="H54" s="57">
-        <v>3</v>
-      </c>
-      <c r="I54" s="57">
-        <v>5</v>
-      </c>
-      <c r="J54" s="57">
-        <v>3</v>
-      </c>
-      <c r="K54" s="57">
-        <v>3</v>
-      </c>
-      <c r="L54" s="57">
-        <v>5</v>
-      </c>
-      <c r="M54" s="57">
-        <v>5</v>
-      </c>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="57"/>
+      <c r="J54" s="57"/>
+      <c r="K54" s="57"/>
+      <c r="L54" s="57"/>
+      <c r="M54" s="57"/>
       <c r="P54" s="57" t="s">
         <v>720</v>
       </c>
@@ -43649,33 +43003,15 @@
       <c r="D55" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E55" s="57">
-        <v>3</v>
-      </c>
-      <c r="F55" s="57">
-        <v>3</v>
-      </c>
-      <c r="G55" s="57">
-        <v>3</v>
-      </c>
-      <c r="H55" s="57">
-        <v>4</v>
-      </c>
-      <c r="I55" s="57">
-        <v>3</v>
-      </c>
-      <c r="J55" s="57">
-        <v>5</v>
-      </c>
-      <c r="K55" s="57">
-        <v>3</v>
-      </c>
-      <c r="L55" s="57">
-        <v>5</v>
-      </c>
-      <c r="M55" s="57">
-        <v>3</v>
-      </c>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="57"/>
+      <c r="M55" s="57"/>
       <c r="P55" s="57"/>
       <c r="Q55" s="59" t="s">
         <v>733</v>
@@ -43773,33 +43109,15 @@
       <c r="D56" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E56" s="57">
-        <v>3</v>
-      </c>
-      <c r="F56" s="57">
-        <v>4</v>
-      </c>
-      <c r="G56" s="57">
-        <v>5</v>
-      </c>
-      <c r="H56" s="57">
-        <v>3</v>
-      </c>
-      <c r="I56" s="57">
-        <v>3</v>
-      </c>
-      <c r="J56" s="57">
-        <v>5</v>
-      </c>
-      <c r="K56" s="57">
-        <v>3</v>
-      </c>
-      <c r="L56" s="57">
-        <v>5</v>
-      </c>
-      <c r="M56" s="57">
-        <v>5</v>
-      </c>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="57"/>
+      <c r="K56" s="57"/>
+      <c r="L56" s="57"/>
+      <c r="M56" s="57"/>
       <c r="P56" s="57"/>
       <c r="Q56" s="59" t="s">
         <v>736</v>
@@ -43858,33 +43176,15 @@
       <c r="D57" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E57" s="57">
-        <v>3</v>
-      </c>
-      <c r="F57" s="57">
-        <v>3</v>
-      </c>
-      <c r="G57" s="57">
-        <v>3</v>
-      </c>
-      <c r="H57" s="57">
-        <v>3</v>
-      </c>
-      <c r="I57" s="57">
-        <v>5</v>
-      </c>
-      <c r="J57" s="57">
-        <v>3</v>
-      </c>
-      <c r="K57" s="57">
-        <v>3</v>
-      </c>
-      <c r="L57" s="57">
-        <v>5</v>
-      </c>
-      <c r="M57" s="57">
-        <v>5</v>
-      </c>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
+      <c r="K57" s="57"/>
+      <c r="L57" s="57"/>
+      <c r="M57" s="57"/>
       <c r="P57" s="57"/>
       <c r="Q57" s="59" t="s">
         <v>739</v>
@@ -43943,33 +43243,17 @@
       <c r="D58" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E58" s="57">
-        <v>5</v>
-      </c>
-      <c r="F58" s="57">
-        <v>5</v>
-      </c>
-      <c r="G58" s="57">
-        <v>5</v>
-      </c>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
       <c r="H58" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="I58" s="57">
-        <v>5</v>
-      </c>
-      <c r="J58" s="57">
-        <v>3</v>
-      </c>
-      <c r="K58" s="57">
-        <v>3</v>
-      </c>
-      <c r="L58" s="57">
-        <v>5</v>
-      </c>
-      <c r="M58" s="57">
-        <v>3</v>
-      </c>
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
+      <c r="K58" s="57"/>
+      <c r="L58" s="57"/>
+      <c r="M58" s="57"/>
       <c r="P58" s="57"/>
       <c r="Q58" s="59" t="s">
         <v>742</v>
@@ -44028,33 +43312,17 @@
       <c r="D59" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E59" s="57">
-        <v>3</v>
-      </c>
-      <c r="F59" s="57">
-        <v>5</v>
-      </c>
-      <c r="G59" s="57">
-        <v>3</v>
-      </c>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
       <c r="H59" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="I59" s="57">
-        <v>5</v>
-      </c>
-      <c r="J59" s="57">
-        <v>3</v>
-      </c>
-      <c r="K59" s="57">
-        <v>3</v>
-      </c>
-      <c r="L59" s="57">
-        <v>5</v>
-      </c>
-      <c r="M59" s="57">
-        <v>5</v>
-      </c>
+      <c r="I59" s="57"/>
+      <c r="J59" s="57"/>
+      <c r="K59" s="57"/>
+      <c r="L59" s="57"/>
+      <c r="M59" s="57"/>
       <c r="P59" s="57"/>
       <c r="Q59" s="59" t="s">
         <v>744</v>
@@ -44105,30 +43373,14 @@
         <v>744</v>
       </c>
       <c r="AK59" s="57"/>
-      <c r="AL59" s="65" t="s">
-        <v>710</v>
-      </c>
-      <c r="AM59" s="65" t="s">
-        <v>711</v>
-      </c>
-      <c r="AN59" s="65" t="s">
-        <v>712</v>
-      </c>
-      <c r="AO59" s="65" t="s">
-        <v>713</v>
-      </c>
-      <c r="AP59" s="65" t="s">
-        <v>714</v>
-      </c>
-      <c r="AQ59" s="65" t="s">
-        <v>715</v>
-      </c>
-      <c r="AR59" s="65" t="s">
-        <v>716</v>
-      </c>
-      <c r="AS59" s="65" t="s">
-        <v>717</v>
-      </c>
+      <c r="AL59" s="65"/>
+      <c r="AM59" s="65"/>
+      <c r="AN59" s="65"/>
+      <c r="AO59" s="65"/>
+      <c r="AP59" s="65"/>
+      <c r="AQ59" s="65"/>
+      <c r="AR59" s="65"/>
+      <c r="AS59" s="65"/>
       <c r="AT59" s="65" t="s">
         <v>718</v>
       </c>
@@ -44143,33 +43395,15 @@
       <c r="D60" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E60" s="57">
-        <v>1</v>
-      </c>
-      <c r="F60" s="57">
-        <v>4</v>
-      </c>
-      <c r="G60" s="57">
-        <v>1</v>
-      </c>
-      <c r="H60" s="57">
-        <v>1</v>
-      </c>
-      <c r="I60" s="57">
-        <v>5</v>
-      </c>
-      <c r="J60" s="57">
-        <v>1</v>
-      </c>
-      <c r="K60" s="57">
-        <v>5</v>
-      </c>
-      <c r="L60" s="57">
-        <v>3</v>
-      </c>
-      <c r="M60" s="57">
-        <v>5</v>
-      </c>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
+      <c r="L60" s="57"/>
+      <c r="M60" s="57"/>
       <c r="P60" s="57" t="s">
         <v>721</v>
       </c>
@@ -44269,33 +43503,15 @@
       <c r="D61" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E61" s="57">
-        <v>3</v>
-      </c>
-      <c r="F61" s="57">
-        <v>4</v>
-      </c>
-      <c r="G61" s="57">
-        <v>4</v>
-      </c>
-      <c r="H61" s="57">
-        <v>4</v>
-      </c>
-      <c r="I61" s="57">
-        <v>3</v>
-      </c>
-      <c r="J61" s="57">
-        <v>4</v>
-      </c>
-      <c r="K61" s="57">
-        <v>3</v>
-      </c>
-      <c r="L61" s="57">
-        <v>4</v>
-      </c>
-      <c r="M61" s="57">
-        <v>5</v>
-      </c>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57"/>
+      <c r="K61" s="57"/>
+      <c r="L61" s="57"/>
+      <c r="M61" s="57"/>
       <c r="P61" s="57"/>
       <c r="Q61" s="59" t="s">
         <v>747</v>
@@ -44393,33 +43609,15 @@
       <c r="D62" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E62" s="57">
-        <v>5</v>
-      </c>
-      <c r="F62" s="57">
-        <v>5</v>
-      </c>
-      <c r="G62" s="57">
-        <v>5</v>
-      </c>
-      <c r="H62" s="57">
-        <v>1</v>
-      </c>
-      <c r="I62" s="57">
-        <v>5</v>
-      </c>
-      <c r="J62" s="57">
-        <v>5</v>
-      </c>
-      <c r="K62" s="57">
-        <v>4</v>
-      </c>
-      <c r="L62" s="57">
-        <v>5</v>
-      </c>
-      <c r="M62" s="57">
-        <v>5</v>
-      </c>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="57"/>
+      <c r="K62" s="57"/>
+      <c r="L62" s="57"/>
+      <c r="M62" s="57"/>
       <c r="P62" s="57"/>
       <c r="Q62" s="59" t="s">
         <v>301</v>
@@ -44519,33 +43717,15 @@
       <c r="D63" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E63" s="57">
-        <v>3</v>
-      </c>
-      <c r="F63" s="57">
-        <v>4</v>
-      </c>
-      <c r="G63" s="57">
-        <v>5</v>
-      </c>
-      <c r="H63" s="57">
-        <v>1</v>
-      </c>
-      <c r="I63" s="57">
-        <v>3</v>
-      </c>
-      <c r="J63" s="57">
-        <v>5</v>
-      </c>
-      <c r="K63" s="57">
-        <v>1</v>
-      </c>
-      <c r="L63" s="57">
-        <v>2</v>
-      </c>
-      <c r="M63" s="57">
-        <v>1</v>
-      </c>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="57"/>
+      <c r="I63" s="57"/>
+      <c r="J63" s="57"/>
+      <c r="K63" s="57"/>
+      <c r="L63" s="57"/>
+      <c r="M63" s="57"/>
       <c r="P63" s="57" t="s">
         <v>722</v>
       </c>
@@ -44606,33 +43786,15 @@
       <c r="D64" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="E64" s="57">
-        <v>4</v>
-      </c>
-      <c r="F64" s="57">
-        <v>4</v>
-      </c>
-      <c r="G64" s="57">
-        <v>4</v>
-      </c>
-      <c r="H64" s="57">
-        <v>5</v>
-      </c>
-      <c r="I64" s="57">
-        <v>4</v>
-      </c>
-      <c r="J64" s="57">
-        <v>4</v>
-      </c>
-      <c r="K64" s="57">
-        <v>2</v>
-      </c>
-      <c r="L64" s="57">
-        <v>4</v>
-      </c>
-      <c r="M64" s="57">
-        <v>3</v>
-      </c>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="57"/>
       <c r="P64" s="57"/>
       <c r="Q64" s="59" t="s">
         <v>754</v>
@@ -44691,33 +43853,15 @@
       <c r="D65" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="E65" s="57">
-        <v>3</v>
-      </c>
-      <c r="F65" s="57">
-        <v>3</v>
-      </c>
-      <c r="G65" s="57">
-        <v>3</v>
-      </c>
-      <c r="H65" s="57">
-        <v>1</v>
-      </c>
-      <c r="I65" s="57">
-        <v>2</v>
-      </c>
-      <c r="J65" s="57">
-        <v>5</v>
-      </c>
-      <c r="K65" s="57">
-        <v>1</v>
-      </c>
-      <c r="L65" s="57">
-        <v>4</v>
-      </c>
-      <c r="M65" s="57">
-        <v>5</v>
-      </c>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="57"/>
+      <c r="K65" s="57"/>
+      <c r="L65" s="57"/>
+      <c r="M65" s="57"/>
       <c r="P65" s="57"/>
       <c r="Q65" s="59" t="s">
         <v>757</v>
@@ -44776,33 +43920,15 @@
       <c r="D66" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="E66" s="57">
-        <v>3</v>
-      </c>
-      <c r="F66" s="57">
-        <v>4</v>
-      </c>
-      <c r="G66" s="57">
-        <v>4</v>
-      </c>
-      <c r="H66" s="57">
-        <v>4</v>
-      </c>
-      <c r="I66" s="57">
-        <v>1</v>
-      </c>
-      <c r="J66" s="57">
-        <v>5</v>
-      </c>
-      <c r="K66" s="57">
-        <v>1</v>
-      </c>
-      <c r="L66" s="57">
-        <v>2</v>
-      </c>
-      <c r="M66" s="57">
-        <v>4</v>
-      </c>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="57"/>
+      <c r="K66" s="57"/>
+      <c r="L66" s="57"/>
+      <c r="M66" s="57"/>
       <c r="P66" s="57"/>
       <c r="Q66" s="59" t="s">
         <v>321</v>
@@ -44861,33 +43987,15 @@
       <c r="D67" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="E67" s="57">
-        <v>5</v>
-      </c>
-      <c r="F67" s="57">
-        <v>5</v>
-      </c>
-      <c r="G67" s="57">
-        <v>5</v>
-      </c>
-      <c r="H67" s="57">
-        <v>1</v>
-      </c>
-      <c r="I67" s="57">
-        <v>5</v>
-      </c>
-      <c r="J67" s="57">
-        <v>5</v>
-      </c>
-      <c r="K67" s="57">
-        <v>5</v>
-      </c>
-      <c r="L67" s="57">
-        <v>5</v>
-      </c>
-      <c r="M67" s="57">
-        <v>5</v>
-      </c>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="57"/>
+      <c r="K67" s="57"/>
+      <c r="L67" s="57"/>
+      <c r="M67" s="57"/>
       <c r="P67" s="57"/>
       <c r="Q67" s="59" t="s">
         <v>762</v>
@@ -44946,33 +44054,17 @@
       <c r="D68" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="E68" s="57">
-        <v>3</v>
-      </c>
-      <c r="F68" s="57">
-        <v>3</v>
-      </c>
-      <c r="G68" s="57">
-        <v>5</v>
-      </c>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
       <c r="H68" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="I68" s="57">
-        <v>5</v>
-      </c>
-      <c r="J68" s="57">
-        <v>5</v>
-      </c>
-      <c r="K68" s="57">
-        <v>3</v>
-      </c>
-      <c r="L68" s="57">
-        <v>2</v>
-      </c>
-      <c r="M68" s="57">
-        <v>2</v>
-      </c>
+      <c r="I68" s="57"/>
+      <c r="J68" s="57"/>
+      <c r="K68" s="57"/>
+      <c r="L68" s="57"/>
+      <c r="M68" s="57"/>
       <c r="P68" s="57"/>
       <c r="Q68" s="59" t="s">
         <v>765</v>
@@ -45031,33 +44123,17 @@
       <c r="D69" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="E69" s="57">
-        <v>4</v>
-      </c>
-      <c r="F69" s="57">
-        <v>5</v>
-      </c>
-      <c r="G69" s="57">
-        <v>3</v>
-      </c>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="57"/>
       <c r="H69" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="I69" s="57">
-        <v>5</v>
-      </c>
-      <c r="J69" s="57">
-        <v>3</v>
-      </c>
-      <c r="K69" s="57">
-        <v>3</v>
-      </c>
-      <c r="L69" s="57">
-        <v>5</v>
-      </c>
-      <c r="M69" s="57">
-        <v>5</v>
-      </c>
+      <c r="I69" s="57"/>
+      <c r="J69" s="57"/>
+      <c r="K69" s="57"/>
+      <c r="L69" s="57"/>
+      <c r="M69" s="57"/>
       <c r="P69" s="57"/>
       <c r="Q69" s="59" t="s">
         <v>768</v>
@@ -45116,33 +44192,17 @@
       <c r="D70" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="E70" s="57">
-        <v>5</v>
-      </c>
-      <c r="F70" s="57">
-        <v>5</v>
-      </c>
-      <c r="G70" s="57">
-        <v>5</v>
-      </c>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
       <c r="H70" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="I70" s="57">
-        <v>5</v>
-      </c>
-      <c r="J70" s="57">
-        <v>3</v>
-      </c>
-      <c r="K70" s="57">
-        <v>5</v>
-      </c>
-      <c r="L70" s="57">
-        <v>5</v>
-      </c>
-      <c r="M70" s="57">
-        <v>2</v>
-      </c>
+      <c r="I70" s="57"/>
+      <c r="J70" s="57"/>
+      <c r="K70" s="57"/>
+      <c r="L70" s="57"/>
+      <c r="M70" s="57"/>
       <c r="P70" s="57"/>
       <c r="Q70" s="59" t="s">
         <v>770</v>
@@ -45201,33 +44261,17 @@
       <c r="D71" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="E71" s="57">
-        <v>5</v>
-      </c>
-      <c r="F71" s="57">
-        <v>5</v>
-      </c>
-      <c r="G71" s="57">
-        <v>5</v>
-      </c>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
       <c r="H71" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="I71" s="57">
-        <v>5</v>
-      </c>
-      <c r="J71" s="57">
-        <v>3</v>
-      </c>
-      <c r="K71" s="57">
-        <v>5</v>
-      </c>
-      <c r="L71" s="57">
-        <v>5</v>
-      </c>
-      <c r="M71" s="57">
-        <v>1</v>
-      </c>
+      <c r="I71" s="57"/>
+      <c r="J71" s="57"/>
+      <c r="K71" s="57"/>
+      <c r="L71" s="57"/>
+      <c r="M71" s="57"/>
       <c r="P71" s="57"/>
       <c r="Q71" s="59" t="s">
         <v>359</v>
@@ -45286,33 +44330,17 @@
       <c r="D72" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="E72" s="57">
-        <v>5</v>
-      </c>
-      <c r="F72" s="57">
-        <v>5</v>
-      </c>
-      <c r="G72" s="57">
-        <v>5</v>
-      </c>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
       <c r="H72" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="I72" s="57">
-        <v>5</v>
-      </c>
-      <c r="J72" s="57">
-        <v>3</v>
-      </c>
-      <c r="K72" s="57">
-        <v>3</v>
-      </c>
-      <c r="L72" s="57">
-        <v>5</v>
-      </c>
-      <c r="M72" s="57">
-        <v>5</v>
-      </c>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="57"/>
+      <c r="L72" s="57"/>
+      <c r="M72" s="57"/>
       <c r="P72" s="57"/>
       <c r="Q72" s="59" t="s">
         <v>774</v>
@@ -45389,15 +44417,9 @@
       <c r="J73" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="K73" s="57">
-        <v>3</v>
-      </c>
-      <c r="L73" s="57">
-        <v>5</v>
-      </c>
-      <c r="M73" s="57">
-        <v>2</v>
-      </c>
+      <c r="K73" s="57"/>
+      <c r="L73" s="57"/>
+      <c r="M73" s="57"/>
       <c r="P73" s="57"/>
       <c r="Q73" s="138" t="s">
         <v>776</v>
@@ -45462,15 +44484,9 @@
       <c r="H74" s="57"/>
       <c r="I74" s="57"/>
       <c r="J74" s="57"/>
-      <c r="K74" s="57">
-        <v>1</v>
-      </c>
-      <c r="L74" s="57">
-        <v>5</v>
-      </c>
-      <c r="M74" s="57">
-        <v>3</v>
-      </c>
+      <c r="K74" s="57"/>
+      <c r="L74" s="57"/>
+      <c r="M74" s="57"/>
       <c r="P74" s="57"/>
       <c r="Q74" s="138" t="s">
         <v>778</v>
@@ -45531,33 +44547,15 @@
       <c r="D75" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E75" s="57">
-        <v>3</v>
-      </c>
-      <c r="F75" s="57">
-        <v>5</v>
-      </c>
-      <c r="G75" s="57">
-        <v>4</v>
-      </c>
-      <c r="H75" s="57">
-        <v>4</v>
-      </c>
-      <c r="I75" s="57">
-        <v>2</v>
-      </c>
-      <c r="J75" s="57">
-        <v>5</v>
-      </c>
-      <c r="K75" s="57">
-        <v>4</v>
-      </c>
-      <c r="L75" s="57">
-        <v>4</v>
-      </c>
-      <c r="M75" s="57">
-        <v>4</v>
-      </c>
+      <c r="E75" s="57"/>
+      <c r="F75" s="57"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="57"/>
+      <c r="J75" s="57"/>
+      <c r="K75" s="57"/>
+      <c r="L75" s="57"/>
+      <c r="M75" s="57"/>
       <c r="P75" s="57" t="s">
         <v>723</v>
       </c>
@@ -45618,33 +44616,15 @@
       <c r="D76" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E76" s="57">
-        <v>4</v>
-      </c>
-      <c r="F76" s="57">
-        <v>5</v>
-      </c>
-      <c r="G76" s="57">
-        <v>4</v>
-      </c>
-      <c r="H76" s="57">
-        <v>2</v>
-      </c>
-      <c r="I76" s="57">
-        <v>2</v>
-      </c>
-      <c r="J76" s="57">
-        <v>5</v>
-      </c>
-      <c r="K76" s="57">
-        <v>2</v>
-      </c>
-      <c r="L76" s="57">
-        <v>5</v>
-      </c>
-      <c r="M76" s="57">
-        <v>4</v>
-      </c>
+      <c r="E76" s="57"/>
+      <c r="F76" s="57"/>
+      <c r="G76" s="57"/>
+      <c r="H76" s="57"/>
+      <c r="I76" s="57"/>
+      <c r="J76" s="57"/>
+      <c r="K76" s="57"/>
+      <c r="L76" s="57"/>
+      <c r="M76" s="57"/>
       <c r="P76" s="57"/>
       <c r="Q76" s="70" t="s">
         <v>781</v>
@@ -45867,27 +44847,17 @@
       <c r="D79" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E79" s="57">
-        <v>2</v>
-      </c>
+      <c r="E79" s="57"/>
       <c r="F79" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="G79" s="57">
-        <v>5</v>
-      </c>
-      <c r="H79" s="57">
-        <v>5</v>
-      </c>
-      <c r="I79" s="57">
-        <v>1</v>
-      </c>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
       <c r="J79" s="57" t="s">
         <v>725</v>
       </c>
-      <c r="K79" s="57">
-        <v>5</v>
-      </c>
+      <c r="K79" s="57"/>
       <c r="L79" s="57" t="s">
         <v>725</v>
       </c>
@@ -45946,33 +44916,15 @@
       <c r="D80" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="E80" s="57">
-        <v>5</v>
-      </c>
-      <c r="F80" s="57">
-        <v>5</v>
-      </c>
-      <c r="G80" s="57">
-        <v>4</v>
-      </c>
-      <c r="H80" s="57">
-        <v>2</v>
-      </c>
-      <c r="I80" s="57">
-        <v>5</v>
-      </c>
-      <c r="J80" s="57">
-        <v>5</v>
-      </c>
-      <c r="K80" s="57">
-        <v>4</v>
-      </c>
-      <c r="L80" s="57">
-        <v>4</v>
-      </c>
-      <c r="M80" s="57">
-        <v>5</v>
-      </c>
+      <c r="E80" s="57"/>
+      <c r="F80" s="57"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="57"/>
+      <c r="I80" s="57"/>
+      <c r="J80" s="57"/>
+      <c r="K80" s="57"/>
+      <c r="L80" s="57"/>
+      <c r="M80" s="57"/>
       <c r="P80" s="57"/>
       <c r="Q80" s="58" t="s">
         <v>423</v>
@@ -49949,9 +48901,7 @@
       <c r="T2" s="487"/>
       <c r="U2" s="487"/>
       <c r="V2" s="487"/>
-      <c r="W2" s="538" t="s">
-        <v>192</v>
-      </c>
+      <c r="W2" s="538"/>
       <c r="X2" s="538"/>
     </row>
     <row r="3" spans="2:25" ht="61" customHeight="1">
@@ -49985,9 +48935,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="526"/>
-      <c r="D4" s="526" t="s">
-        <v>196</v>
-      </c>
+      <c r="D4" s="526"/>
       <c r="E4" s="526"/>
       <c r="F4" s="526"/>
       <c r="G4" s="526"/>
@@ -57612,9 +56560,7 @@
  *At least, need to check its progress within 1 year.
 (Safety Manager)</v>
       </c>
-      <c r="J11" s="12" t="s">
-        <v>651</v>
-      </c>
+      <c r="J11" s="12"/>
     </row>
     <row r="12" spans="2:11" ht="49.5">
       <c r="C12" s="548"/>
@@ -58688,9 +57634,7 @@
         <v>OH&amp;S policy has been established at site. And the manager can explain it.
 (System: Plant Manager: No.9)</v>
       </c>
-      <c r="J7" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" spans="2:10" ht="33">
       <c r="C8" s="550"/>
@@ -58709,9 +57653,7 @@
         <v>Management can describe and explain the site's OH&amp;S objectives and goals.
 (System: Manager: No.66)</v>
       </c>
-      <c r="J8" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" spans="2:10" ht="49.5">
       <c r="C9" s="550"/>
@@ -58730,9 +57672,7 @@
         <v>The plan contains goals to be achieved which are relevant to the incidents and risks identified by the SBU.
 (System: Manager: No.98)</v>
       </c>
-      <c r="J9" s="29" t="s">
-        <v>651</v>
-      </c>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" spans="2:10" ht="33">
       <c r="C10" s="550"/>
@@ -60134,9 +59074,7 @@
         <v>Autonomously KY has not been conducted.
 (SVs)</v>
       </c>
-      <c r="J33" s="24" t="s">
-        <v>651</v>
-      </c>
+      <c r="J33" s="24"/>
     </row>
     <row r="34" spans="3:10" ht="49.5">
       <c r="C34" s="550"/>
